--- a/questionnaire_templates/033_event_logistics_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/033_event_logistics_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>eventLogisticsAssessment</t>
+          <t>Event Logistics Assessment Questionnaire 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
